--- a/Cluster_Features.xlsx
+++ b/Cluster_Features.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="139">
   <si>
     <t>Reference key for cluster feature sources</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>In Optimized Probit Model</t>
   </si>
   <si>
     <t>Life Cycle</t>
@@ -446,12 +449,20 @@
 S15 = FY - 15</t>
   </si>
   <si>
+    <t>S1 - S6, S9: TRUE;
+S8, S10 - S15: FALSE</t>
+  </si>
+  <si>
     <t>dS0 - dS14</t>
   </si>
   <si>
     <t>Change in Share
 Change in a cluster’s yearly share of articles. For example, 
 dS0 = S0 - S1</t>
+  </si>
+  <si>
+    <t>dS1, dS2-dS4, dS6, dS7, dS9: TRUE
+dS0, dS5, dS8, dS10-dS14: FALSE</t>
   </si>
   <si>
     <t>Citation Shares</t>
@@ -468,12 +479,20 @@
 CS15 = FY - 15</t>
   </si>
   <si>
+    <t>CS1 - CS3, CS13: TRUE
+CS4 - CS12, CS14: FALSE</t>
+  </si>
+  <si>
     <t>dCS0 - dCS14</t>
   </si>
   <si>
     <t>Change in Share of Citations
 Change in a cluster’s yearly share of citations. For example, 
 dCS0 = CS0 - CS1</t>
+  </si>
+  <si>
+    <t>dCS0, dCS1, dCS6, dCS13, dCS14: TRUE
+dCS2 - dCS5, dCS7 - dCS12: FALSE</t>
   </si>
   <si>
     <t>Reference Shares</t>
@@ -490,12 +509,21 @@
 CS15 = FY - 15</t>
   </si>
   <si>
+    <t>RS0, RS1, RS4, RS7: TRUE;
+RS2, RS3, RS5, RS6, RS8 - RS14: FALSE</t>
+  </si>
+  <si>
     <t>DRS0 - dRS14</t>
   </si>
   <si>
     <t>Change in Share of References
 Change in a cluster’s yearly share of citations. For example, 
 dCS0 = CS0 - CS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dRS1 - dRS4, dRS6: TRUE
+dRS0, dRS5, dRS7 - dRS15: FALSE
+</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1222,9 @@
       <c r="E13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="2"/>
+      <c r="F13" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -1218,21 +1248,23 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
-      <c r="F14" s="2"/>
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1256,18 +1288,20 @@
     </row>
     <row r="15">
       <c r="B15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>31</v>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1291,18 +1325,20 @@
     </row>
     <row r="16">
       <c r="B16" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="2"/>
+      <c r="F16" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -1326,18 +1362,20 @@
     </row>
     <row r="17">
       <c r="B17" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
-      <c r="F17" s="2"/>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -1361,18 +1399,20 @@
     </row>
     <row r="18">
       <c r="B18" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="2"/>
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1396,18 +1436,20 @@
     </row>
     <row r="19">
       <c r="B19" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="2"/>
+      <c r="F19" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -1431,18 +1473,20 @@
     </row>
     <row r="20">
       <c r="B20" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="2"/>
+      <c r="F20" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -1466,18 +1510,20 @@
     </row>
     <row r="21">
       <c r="B21" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="2"/>
+      <c r="F21" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -1501,18 +1547,20 @@
     </row>
     <row r="22">
       <c r="B22" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="2"/>
+      <c r="F22" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -1536,18 +1584,20 @@
     </row>
     <row r="23">
       <c r="B23" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="2"/>
+      <c r="F23" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -1571,18 +1621,20 @@
     </row>
     <row r="24">
       <c r="B24" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="2"/>
+      <c r="F24" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -1606,18 +1658,20 @@
     </row>
     <row r="25">
       <c r="B25" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="2"/>
+      <c r="F25" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -1641,18 +1695,20 @@
     </row>
     <row r="26">
       <c r="B26" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="2"/>
+      <c r="F26" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -1676,18 +1732,20 @@
     </row>
     <row r="27">
       <c r="B27" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F27" s="2"/>
+      <c r="F27" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -1711,18 +1769,20 @@
     </row>
     <row r="28">
       <c r="B28" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="2"/>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -1746,18 +1806,20 @@
     </row>
     <row r="29">
       <c r="B29" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="2"/>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -1781,21 +1843,23 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
-      <c r="F30" s="2"/>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -1819,18 +1883,20 @@
     </row>
     <row r="31">
       <c r="B31" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>69</v>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -1854,21 +1920,23 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
-      <c r="F32" s="2"/>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -1892,18 +1960,20 @@
     </row>
     <row r="33">
       <c r="B33" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
-      <c r="F33" s="2"/>
+      <c r="F33" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -1927,18 +1997,20 @@
     </row>
     <row r="34">
       <c r="B34" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
-      <c r="F34" s="2"/>
+      <c r="F34" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -1962,18 +2034,20 @@
     </row>
     <row r="35">
       <c r="B35" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="2"/>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -1997,21 +2071,23 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F36" s="2"/>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -2035,21 +2111,23 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="2"/>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -2073,18 +2151,20 @@
     </row>
     <row r="38">
       <c r="B38" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="2"/>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -2108,18 +2188,20 @@
     </row>
     <row r="39">
       <c r="B39" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F39" s="2"/>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -2143,18 +2225,20 @@
     </row>
     <row r="40">
       <c r="B40" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="2"/>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -2178,18 +2262,20 @@
     </row>
     <row r="41">
       <c r="B41" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F41" s="2"/>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -2213,18 +2299,20 @@
     </row>
     <row r="42">
       <c r="B42" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F42" s="2"/>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
@@ -2248,18 +2336,20 @@
     </row>
     <row r="43">
       <c r="B43" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F43" s="2"/>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -2283,21 +2373,23 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="2"/>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
@@ -2321,21 +2413,23 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F45" s="2"/>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -2359,18 +2453,20 @@
     </row>
     <row r="46">
       <c r="B46" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F46" s="2"/>
+      <c r="F46" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -2394,18 +2490,20 @@
     </row>
     <row r="47">
       <c r="B47" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F47" s="2"/>
+      <c r="F47" s="4" t="b">
+        <v>0</v>
+      </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
@@ -2429,21 +2527,23 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F48" s="2"/>
+      <c r="F48" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -2467,18 +2567,20 @@
     </row>
     <row r="49">
       <c r="B49" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
-      <c r="F49" s="2"/>
+      <c r="F49" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
@@ -2502,18 +2604,20 @@
     </row>
     <row r="50">
       <c r="B50" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C50" s="8" t="s">
-        <v>116</v>
+      <c r="F50" s="4" t="b">
+        <v>1</v>
       </c>
-      <c r="D50" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -2537,21 +2641,23 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F51" s="2"/>
+      <c r="F51" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -2575,18 +2681,20 @@
     </row>
     <row r="52">
       <c r="B52" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F52" s="2"/>
+      <c r="F52" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -2610,21 +2718,23 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F53" s="2"/>
+      <c r="F53" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -2648,18 +2758,20 @@
     </row>
     <row r="54">
       <c r="B54" s="8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F54" s="2"/>
+      <c r="F54" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -2683,21 +2795,23 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F55" s="2"/>
+      <c r="F55" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -2721,18 +2835,20 @@
     </row>
     <row r="56">
       <c r="B56" s="8" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F56" s="2"/>
+      <c r="F56" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
@@ -29160,6 +29276,8 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A51:A52"/>
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="A1:E1"/>
@@ -29169,8 +29287,6 @@
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A37:A43"/>
     <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A52"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B3"/>
